--- a/frontend/public/plantilla_ingredientes.xlsx
+++ b/frontend/public/plantilla_ingredientes.xlsx
@@ -1,11 +1,19 @@
 
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Ingredientes" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>VARAGRILL — PLANTILLA DE CARGA DE INGREDIENTES</t>
   </si>
   <si>
-    <t>Completa Ingrediente, Unidad (kg, g, l, ml o unidad) y Cantidad. Deja la Cantidad vacía o en 0 en el ingrediente que NO quieras actualizar en esta carga — esa fila se ignora.</t>
+    <t>Completa Ingrediente, Unidad (g, ml o unidad) y Cantidad. Deja la Cantidad vacía o en 0 en el ingrediente que NO quieras actualizar en esta carga — esa fila se ignora.</t>
   </si>
   <si>
     <t>Ingrediente</t>
@@ -20,12 +28,12 @@
     <t>Tomate (ejemplo — reemplaza o borra esta fila)</t>
   </si>
   <si>
-    <t>kg</t>
+    <t>g</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="4">
     <font>
@@ -88,15 +96,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Ingredientes" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -140,7 +140,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="0">
-        <v>20.5</v>
+        <v>20500</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/plantilla_ingredientes.xlsx
+++ b/frontend/public/plantilla_ingredientes.xlsx
@@ -8,12 +8,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>VARAGRILL — PLANTILLA DE CARGA DE INGREDIENTES</t>
   </si>
   <si>
-    <t>Completa Ingrediente, Unidad (g, ml o unidad) y Cantidad. Deja la Cantidad vacía o en 0 en el ingrediente que NO quieras actualizar en esta carga — esa fila se ignora.</t>
+    <t>Completa Ingrediente, Unidad (g, ml o unidad) y Cantidad. Deja la Cantidad vacía o en 0 en el ingrediente que NO quieras actualizar en esta carga — esa fila se ignora. Si además completas Peso neto, Peso real y Precio de compra (las tres juntas), el costo unitario se calcula solo; para un ingrediente que ya existe, esas tres columnas pueden ir solas, sin Cantidad, para actualizar el costeo sin hacer un reconteo.</t>
   </si>
   <si>
     <t>Ingrediente</t>
@@ -29,6 +29,15 @@
   </si>
   <si>
     <t>g</t>
+  </si>
+  <si>
+    <t>Peso neto</t>
+  </si>
+  <si>
+    <t>Peso real</t>
+  </si>
+  <si>
+    <t>Precio de compra</t>
   </si>
 </sst>
 </file>
@@ -98,30 +107,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1">
+    <row r="1" spans="1:6" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:3" ht="30" customHeight="1">
+    <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:3"/>
-    <row r="4" spans="1:3">
+    <row r="3" spans="1:6"/>
+    <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -131,8 +149,17 @@
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="0" t="s">
         <v>5</v>
       </c>
@@ -142,11 +169,20 @@
       <c r="C5" s="0">
         <v>20500</v>
       </c>
+      <c r="D5" s="0">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="0">
+        <v>900</v>
+      </c>
+      <c r="F5" s="0">
+        <v>8500</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
